--- a/2.Hardware/1.PCB/1.MainBoard/6.BOM/MainBoard.xlsx
+++ b/2.Hardware/1.PCB/1.MainBoard/6.BOM/MainBoard.xlsx
@@ -3426,8 +3426,8 @@
         <v>237</v>
       </c>
       <c r="F64" s="1">
-        <f>SUM(F2:F63)</f>
-        <v>375530</v>
+        <f>SUM(F2:F63)-4*E63</f>
+        <v>269930</v>
       </c>
     </row>
   </sheetData>
@@ -3496,6 +3496,7 @@
     <hyperlink ref="G63" r:id="rId57" display="https://shopee.vn/S%E1%BA%A3n-xu%E1%BA%A5t-PCB-ch%E1%BA%A5t-l%C6%B0%E1%BB%A3ng-cao-%E2%80%93-MOQ-5-T%C3%B9y-ch%E1%BB%89nh-m%C3%A0u-mi%E1%BB%85n-ph%C3%AD-B%E1%BA%A3ng-%C4%91%C6%A1n-%C4%91%C3%B4i-v%C3%A0-nhi%E1%BB%81u-l%E1%BB%9Bp-i.1135296432.28315488514"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/2.Hardware/1.PCB/1.MainBoard/6.BOM/MainBoard.xlsx
+++ b/2.Hardware/1.PCB/1.MainBoard/6.BOM/MainBoard.xlsx
@@ -740,7 +740,7 @@
     <t>https://shopee.vn/S%E1%BA%A3n-xu%E1%BA%A5t-PCB-ch%E1%BA%A5t-l%C6%B0%E1%BB%A3ng-cao-%E2%80%93-MOQ-5-T%C3%B9y-ch%E1%BB%89nh-m%C3%A0u-mi%E1%BB%85n-ph%C3%AD-B%E1%BA%A3ng-%C4%91%C6%A1n-%C4%91%C3%B4i-v%C3%A0-nhi%E1%BB%81u-l%E1%BB%9Bp-i.1135296432.28315488514</t>
   </si>
   <si>
-    <t>Tổng tiền</t>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -754,8 +754,16 @@
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="[$VND]\ #,##0.00;[$VND]\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -776,6 +784,14 @@
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1227,147 +1243,156 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -1917,30 +1942,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -1952,19 +1977,19 @@
       <c r="D2">
         <v>9</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="2">
         <v>190</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="2">
         <f t="shared" ref="F2:F12" si="0">E2*D2</f>
         <v>1710</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
@@ -1976,19 +2001,19 @@
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" s="2">
         <v>400</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="2">
         <f t="shared" si="0"/>
         <v>400</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
@@ -2000,19 +2025,19 @@
       <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="2">
         <v>1500</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="2">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
@@ -2024,19 +2049,19 @@
       <c r="D5">
         <v>3</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E5" s="2">
         <v>190</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>570</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B6" t="s">
@@ -2048,19 +2073,19 @@
       <c r="D6">
         <v>2</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="2">
         <v>350</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>700</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="7" t="s">
         <v>27</v>
       </c>
       <c r="B7" t="s">
@@ -2072,19 +2097,19 @@
       <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="2">
         <v>190</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>1140</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
@@ -2096,19 +2121,19 @@
       <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="2">
         <v>190</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="7" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
@@ -2120,19 +2145,19 @@
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="1">
+      <c r="E9" s="2">
         <v>500</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>500</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
@@ -2144,19 +2169,19 @@
       <c r="D10">
         <v>4</v>
       </c>
-      <c r="E10" s="1">
-        <v>192</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="E10" s="2">
+        <v>190</v>
+      </c>
+      <c r="F10" s="2">
         <f t="shared" si="0"/>
-        <v>768</v>
-      </c>
-      <c r="G10" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="7" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -2168,19 +2193,19 @@
       <c r="D11">
         <v>1</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="2">
         <v>800</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="2">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="7" t="s">
         <v>46</v>
       </c>
       <c r="B12" t="s">
@@ -2192,19 +2217,19 @@
       <c r="D12">
         <v>1</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="2">
         <v>800</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="2">
         <f t="shared" si="0"/>
         <v>800</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B13" t="s">
@@ -2216,19 +2241,19 @@
       <c r="D13">
         <v>6</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="2">
         <v>600</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="2">
         <f>E13*D9</f>
         <v>600</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="3" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B14" t="s">
@@ -2240,14 +2265,14 @@
       <c r="D14">
         <v>1</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="2">
         <v>400</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="2">
         <f>E14*D11</f>
         <v>400</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="G14" s="3" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2264,14 +2289,14 @@
       <c r="D15">
         <v>4</v>
       </c>
-      <c r="E15" s="1">
+      <c r="E15" s="2">
         <v>180</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="2">
         <f t="shared" ref="F15:F60" si="1">E15*D15</f>
         <v>720</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="G15" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -2288,14 +2313,14 @@
       <c r="D16">
         <v>2</v>
       </c>
-      <c r="E16" s="1">
+      <c r="E16" s="2">
         <v>500</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="2">
         <f t="shared" si="1"/>
         <v>1000</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="G16" s="3" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2312,14 +2337,14 @@
       <c r="D17">
         <v>2</v>
       </c>
-      <c r="E17" s="1">
+      <c r="E17" s="2">
         <v>200</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="2">
         <f t="shared" si="1"/>
         <v>400</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="G17" s="3" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2336,14 +2361,14 @@
       <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="1">
+      <c r="E18" s="2">
         <v>600</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="2">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="G18" s="3" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2360,14 +2385,14 @@
       <c r="D19">
         <v>2</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E19" s="2">
         <v>350</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="2">
         <f t="shared" si="1"/>
         <v>700</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G19" s="3" t="s">
         <v>77</v>
       </c>
     </row>
@@ -2384,14 +2409,14 @@
       <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E20" s="2">
         <v>170</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="2">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="G20" s="3" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2408,14 +2433,14 @@
       <c r="D21">
         <v>1</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="2">
         <v>210</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="2">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2432,19 +2457,19 @@
       <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22" s="1">
+      <c r="E22" s="2">
         <v>180</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="2">
         <f t="shared" si="1"/>
         <v>180</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="7" t="s">
         <v>89</v>
       </c>
       <c r="B23" t="s">
@@ -2456,19 +2481,19 @@
       <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" s="1">
+      <c r="E23" s="2">
         <v>1500</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="7" t="s">
         <v>93</v>
       </c>
       <c r="B24" t="s">
@@ -2480,19 +2505,19 @@
       <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" s="1">
+      <c r="E24" s="2">
         <v>1700</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="2">
         <f t="shared" si="1"/>
         <v>1700</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="7" t="s">
         <v>97</v>
       </c>
       <c r="B25" t="s">
@@ -2504,19 +2529,19 @@
       <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25" s="1">
+      <c r="E25" s="2">
         <v>1500</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="7" t="s">
         <v>101</v>
       </c>
       <c r="B26" t="s">
@@ -2528,14 +2553,14 @@
       <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26" s="1">
+      <c r="E26" s="2">
         <v>3000</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="2">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2552,14 +2577,14 @@
       <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27" s="1">
+      <c r="E27" s="2">
         <v>600</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="2">
         <f t="shared" si="1"/>
         <v>600</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" s="3" t="s">
         <v>108</v>
       </c>
     </row>
@@ -2576,14 +2601,14 @@
       <c r="D28">
         <v>1</v>
       </c>
-      <c r="E28" s="1">
+      <c r="E28" s="2">
         <v>1500</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="G28" s="3" t="s">
         <v>112</v>
       </c>
     </row>
@@ -2600,14 +2625,14 @@
       <c r="D29">
         <v>1</v>
       </c>
-      <c r="E29" s="1">
+      <c r="E29" s="2">
         <v>3000</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="2">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" s="3" t="s">
         <v>116</v>
       </c>
     </row>
@@ -2624,14 +2649,14 @@
       <c r="D30">
         <v>3</v>
       </c>
-      <c r="E30" s="1">
+      <c r="E30" s="2">
         <v>4200</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="2">
         <f t="shared" si="1"/>
         <v>12600</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G30" s="3" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2648,14 +2673,14 @@
       <c r="D31">
         <v>1</v>
       </c>
-      <c r="E31" s="1">
+      <c r="E31" s="2">
         <v>3500</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="2">
         <f t="shared" si="1"/>
         <v>3500</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="G31" s="3" t="s">
         <v>123</v>
       </c>
     </row>
@@ -2672,14 +2697,14 @@
       <c r="D32">
         <v>1</v>
       </c>
-      <c r="E32" s="1">
+      <c r="E32" s="2">
         <v>3700</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="2">
         <f t="shared" si="1"/>
         <v>3700</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="3" t="s">
         <v>126</v>
       </c>
     </row>
@@ -2696,14 +2721,14 @@
       <c r="D33">
         <v>1</v>
       </c>
-      <c r="E33" s="1">
+      <c r="E33" s="2">
         <v>800</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="2">
         <f t="shared" si="1"/>
         <v>800</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="G33" s="3" t="s">
         <v>129</v>
       </c>
     </row>
@@ -2720,14 +2745,14 @@
       <c r="D34">
         <v>2</v>
       </c>
-      <c r="E34" s="1">
+      <c r="E34" s="2">
         <v>1200</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="2">
         <f t="shared" si="1"/>
         <v>2400</v>
       </c>
-      <c r="G34" s="2" t="s">
+      <c r="G34" s="3" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2744,14 +2769,14 @@
       <c r="D35">
         <v>1</v>
       </c>
-      <c r="E35" s="1">
+      <c r="E35" s="2">
         <v>4500</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="2">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="G35" s="3" t="s">
+      <c r="G35" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2768,14 +2793,14 @@
       <c r="D36">
         <v>1</v>
       </c>
-      <c r="E36" s="1">
+      <c r="E36" s="2">
         <v>1300</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="2">
         <f t="shared" si="1"/>
         <v>1300</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2792,14 +2817,14 @@
       <c r="D37">
         <v>1</v>
       </c>
-      <c r="E37" s="1">
+      <c r="E37" s="2">
         <v>4500</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="2">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="G37" s="3" t="s">
+      <c r="G37" s="4" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2816,19 +2841,19 @@
       <c r="D38">
         <v>3</v>
       </c>
-      <c r="E38" s="1">
+      <c r="E38" s="2">
         <v>1200</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="2">
         <f t="shared" si="1"/>
         <v>3600</v>
       </c>
-      <c r="G38" s="3" t="s">
+      <c r="G38" s="4" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="39" spans="1:7">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="7" t="s">
         <v>143</v>
       </c>
       <c r="B39" t="s">
@@ -2840,19 +2865,19 @@
       <c r="D39">
         <v>3</v>
       </c>
-      <c r="E39" s="1">
+      <c r="E39" s="2">
         <v>900</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="2">
         <f t="shared" si="1"/>
         <v>2700</v>
       </c>
-      <c r="G39" s="3" t="s">
+      <c r="G39" s="4" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="7" t="s">
         <v>147</v>
       </c>
       <c r="B40" t="s">
@@ -2864,19 +2889,19 @@
       <c r="D40">
         <v>3</v>
       </c>
-      <c r="E40" s="1">
+      <c r="E40" s="2">
         <v>1200</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="2">
         <f t="shared" si="1"/>
         <v>3600</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="3" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" s="4" t="s">
+      <c r="A41" s="7" t="s">
         <v>151</v>
       </c>
       <c r="B41" t="s">
@@ -2888,14 +2913,14 @@
       <c r="D41">
         <v>5</v>
       </c>
-      <c r="E41" s="1">
+      <c r="E41" s="2">
         <v>680</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="2">
         <f t="shared" si="1"/>
         <v>3400</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="G41" s="3" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2912,14 +2937,14 @@
       <c r="D42">
         <v>1</v>
       </c>
-      <c r="E42" s="1">
+      <c r="E42" s="2">
         <v>4500</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="2">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G42" s="3" t="s">
         <v>135</v>
       </c>
     </row>
@@ -2936,14 +2961,14 @@
       <c r="D43">
         <v>2</v>
       </c>
-      <c r="E43" s="1">
+      <c r="E43" s="2">
         <v>1500</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="2">
         <f t="shared" si="1"/>
         <v>3000</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G43" s="3" t="s">
         <v>159</v>
       </c>
     </row>
@@ -2960,19 +2985,19 @@
       <c r="D44">
         <v>3</v>
       </c>
-      <c r="E44" s="1">
+      <c r="E44" s="2">
         <v>2000</v>
       </c>
-      <c r="F44" s="1">
+      <c r="F44" s="2">
         <f t="shared" si="1"/>
         <v>6000</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="4" t="s">
+      <c r="A45" s="7" t="s">
         <v>164</v>
       </c>
       <c r="B45" t="s">
@@ -2984,19 +3009,19 @@
       <c r="D45">
         <v>18</v>
       </c>
-      <c r="E45" s="1">
+      <c r="E45" s="2">
         <v>38</v>
       </c>
-      <c r="F45" s="1">
+      <c r="F45" s="2">
         <f t="shared" si="1"/>
         <v>684</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="7" t="s">
         <v>168</v>
       </c>
       <c r="B46" t="s">
@@ -3008,19 +3033,19 @@
       <c r="D46">
         <v>5</v>
       </c>
-      <c r="E46" s="1">
+      <c r="E46" s="2">
         <v>38</v>
       </c>
-      <c r="F46" s="1">
+      <c r="F46" s="2">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:7">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="7" t="s">
         <v>172</v>
       </c>
       <c r="B47" t="s">
@@ -3032,19 +3057,19 @@
       <c r="D47">
         <v>7</v>
       </c>
-      <c r="E47" s="1">
+      <c r="E47" s="2">
         <v>38</v>
       </c>
-      <c r="F47" s="1">
+      <c r="F47" s="2">
         <f t="shared" si="1"/>
         <v>266</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="G47" s="4" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:7">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="7" t="s">
         <v>176</v>
       </c>
       <c r="B48" t="s">
@@ -3056,19 +3081,19 @@
       <c r="D48">
         <v>3</v>
       </c>
-      <c r="E48" s="1">
+      <c r="E48" s="2">
         <v>50</v>
       </c>
-      <c r="F48" s="1">
+      <c r="F48" s="2">
         <f t="shared" si="1"/>
         <v>150</v>
       </c>
-      <c r="G48" s="3" t="s">
+      <c r="G48" s="4" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" s="4" t="s">
+      <c r="A49" s="7" t="s">
         <v>180</v>
       </c>
       <c r="B49" t="s">
@@ -3080,19 +3105,19 @@
       <c r="D49">
         <v>1</v>
       </c>
-      <c r="E49" s="1">
+      <c r="E49" s="2">
         <v>32</v>
       </c>
-      <c r="F49" s="1">
+      <c r="F49" s="2">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="G49" s="4" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:7">
-      <c r="A50" s="4" t="s">
+      <c r="A50" s="7" t="s">
         <v>184</v>
       </c>
       <c r="B50" t="s">
@@ -3104,19 +3129,19 @@
       <c r="D50">
         <v>1</v>
       </c>
-      <c r="E50" s="1">
+      <c r="E50" s="2">
         <v>38</v>
       </c>
-      <c r="F50" s="1">
+      <c r="F50" s="2">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" s="3" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:7">
-      <c r="A51" s="4" t="s">
+      <c r="A51" s="7" t="s">
         <v>188</v>
       </c>
       <c r="B51" t="s">
@@ -3128,19 +3153,19 @@
       <c r="D51">
         <v>1</v>
       </c>
-      <c r="E51" s="1">
+      <c r="E51" s="2">
         <v>32</v>
       </c>
-      <c r="F51" s="1">
+      <c r="F51" s="2">
         <f t="shared" si="1"/>
         <v>32</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" s="3" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:7">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="7" t="s">
         <v>192</v>
       </c>
       <c r="B52" t="s">
@@ -3152,19 +3177,19 @@
       <c r="D52">
         <v>2</v>
       </c>
-      <c r="E52" s="1">
+      <c r="E52" s="2">
         <v>32</v>
       </c>
-      <c r="F52" s="1">
+      <c r="F52" s="2">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" s="3" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:7">
-      <c r="A53" s="4" t="s">
+      <c r="A53" s="7" t="s">
         <v>196</v>
       </c>
       <c r="B53" t="s">
@@ -3176,14 +3201,14 @@
       <c r="D53">
         <v>3</v>
       </c>
-      <c r="E53" s="1">
+      <c r="E53" s="2">
         <v>32</v>
       </c>
-      <c r="F53" s="1">
+      <c r="F53" s="2">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" s="3" t="s">
         <v>199</v>
       </c>
     </row>
@@ -3200,19 +3225,19 @@
       <c r="D54">
         <v>4</v>
       </c>
-      <c r="E54" s="1">
+      <c r="E54" s="2">
         <v>380</v>
       </c>
-      <c r="F54" s="1">
+      <c r="F54" s="2">
         <f t="shared" si="1"/>
         <v>1520</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" s="3" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="55" spans="1:7">
-      <c r="A55" s="4" t="s">
+      <c r="A55" s="7" t="s">
         <v>204</v>
       </c>
       <c r="B55" t="s">
@@ -3224,14 +3249,14 @@
       <c r="D55">
         <v>3</v>
       </c>
-      <c r="E55" s="1">
+      <c r="E55" s="2">
         <v>500</v>
       </c>
-      <c r="F55" s="1">
+      <c r="F55" s="2">
         <f t="shared" si="1"/>
         <v>1500</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" s="3" t="s">
         <v>207</v>
       </c>
     </row>
@@ -3248,14 +3273,14 @@
       <c r="D56">
         <v>1</v>
       </c>
-      <c r="E56" s="1">
+      <c r="E56" s="2">
         <v>85000</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="2">
         <f t="shared" si="1"/>
         <v>85000</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="G56" s="3" t="s">
         <v>211</v>
       </c>
     </row>
@@ -3272,14 +3297,14 @@
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="E57" s="1">
+      <c r="E57" s="2">
         <v>13000</v>
       </c>
-      <c r="F57" s="1">
+      <c r="F57" s="2">
         <f t="shared" si="1"/>
         <v>13000</v>
       </c>
-      <c r="G57" s="2" t="s">
+      <c r="G57" s="3" t="s">
         <v>215</v>
       </c>
     </row>
@@ -3296,14 +3321,14 @@
       <c r="D58">
         <v>1</v>
       </c>
-      <c r="E58" s="1">
+      <c r="E58" s="2">
         <v>3500</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="2">
         <f t="shared" si="1"/>
         <v>3500</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G58" s="3" t="s">
         <v>219</v>
       </c>
     </row>
@@ -3320,14 +3345,14 @@
       <c r="D59">
         <v>1</v>
       </c>
-      <c r="E59" s="1">
+      <c r="E59" s="2">
         <v>33000</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="2">
         <f t="shared" si="1"/>
         <v>33000</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="4" t="s">
         <v>223</v>
       </c>
     </row>
@@ -3344,14 +3369,14 @@
       <c r="D60">
         <v>2</v>
       </c>
-      <c r="E60" s="1">
+      <c r="E60" s="2">
         <v>4000</v>
       </c>
-      <c r="F60" s="1">
+      <c r="F60" s="2">
         <f t="shared" si="1"/>
         <v>8000</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="3" t="s">
         <v>227</v>
       </c>
     </row>
@@ -3365,14 +3390,14 @@
       <c r="D61">
         <v>1</v>
       </c>
-      <c r="E61" s="1">
+      <c r="E61" s="2">
         <v>4000</v>
       </c>
-      <c r="F61" s="1">
+      <c r="F61" s="2">
         <f>E61*D62</f>
         <v>4000</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="G61" s="3" t="s">
         <v>230</v>
       </c>
     </row>
@@ -3389,14 +3414,14 @@
       <c r="D62">
         <v>1</v>
       </c>
-      <c r="E62" s="1">
+      <c r="E62" s="2">
         <v>4000</v>
       </c>
-      <c r="F62" s="1">
+      <c r="F62" s="2">
         <f>E62*D62</f>
         <v>4000</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="4" t="s">
         <v>234</v>
       </c>
     </row>
@@ -3410,24 +3435,24 @@
       <c r="D63">
         <v>5</v>
       </c>
-      <c r="E63" s="1">
-        <v>26400</v>
-      </c>
-      <c r="F63" s="1">
+      <c r="E63" s="2">
+        <v>20000</v>
+      </c>
+      <c r="F63" s="2">
         <f>E63*D63</f>
-        <v>132000</v>
-      </c>
-      <c r="G63" s="2" t="s">
+        <v>100000</v>
+      </c>
+      <c r="G63" s="3" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="64" spans="5:6">
-      <c r="E64" t="s">
+      <c r="E64" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F64" s="1">
+      <c r="F64" s="6">
         <f>SUM(F2:F63)-4*E63</f>
-        <v>269930</v>
+        <v>263522</v>
       </c>
     </row>
   </sheetData>
